--- a/database.xlsx
+++ b/database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tfahey/github/veracode-tags-test/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://veracode-my.sharepoint.com/personal/rpereira_veracode_com/Documents/Projects/plugins/veracode-tags-test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E0D05FF-5725-1243-B41D-A617284D362D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="13_ncr:1_{6E0D05FF-5725-1243-B41D-A617284D362D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F48E9F9D-652F-4CEB-A142-CEB78ABB6819}"/>
   <bookViews>
-    <workbookView xWindow="37400" yWindow="500" windowWidth="34560" windowHeight="20520" xr2:uid="{2F78EC58-0DE5-4912-881B-95C7E8275247}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2F78EC58-0DE5-4912-881B-95C7E8275247}"/>
   </bookViews>
   <sheets>
     <sheet name="database" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1127" uniqueCount="787">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="823">
   <si>
     <t>repo-url</t>
   </si>
@@ -2405,13 +2405,141 @@
   </si>
   <si>
     <t>Scan Results, User Management, Bulk Processing, Historic Data, Automation Script</t>
+  </si>
+  <si>
+    <t>cadonuno</t>
+  </si>
+  <si>
+    <t>https://github.com/cadonuno/veracode-get-next-safe-for-all-vulnerable-libraries</t>
+  </si>
+  <si>
+    <t>Veracode Get SCA Safe Versions</t>
+  </si>
+  <si>
+    <t>A small plugin which downloads the latest scan for an application/sandbox and saves the SCA results (including a list of safe versions) to a CSV file</t>
+  </si>
+  <si>
+    <t>https://github.com/cadonuno/veracode-bulk-sbom-python</t>
+  </si>
+  <si>
+    <t>Veracode Bulk SBOM - Python</t>
+  </si>
+  <si>
+    <t>A small plugin that fetches all SBOMs available to the current user</t>
+  </si>
+  <si>
+    <t>https://github.com/cadonuno/veracode-policy-results-to-pipeline-json</t>
+  </si>
+  <si>
+    <t>Veracode Policy Results to Pipeline JSON</t>
+  </si>
+  <si>
+    <t>A small plugin that converts Veracode policy scan results into the equivalent pipeline scan output (for usage with Veracode Fix)</t>
+  </si>
+  <si>
+    <t>Scan Results, SAST, Plugin</t>
+  </si>
+  <si>
+    <t>Scan Results, SCA, SBOM, Automation Script</t>
+  </si>
+  <si>
+    <t>https://github.com/cadonuno/veracode-get-all-scan-reports</t>
+  </si>
+  <si>
+    <r>
+      <t>This repository contains </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>get-all-reports.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, a utility script for downloading all available Veracode scan reports</t>
+    </r>
+  </si>
+  <si>
+    <t>Veracode Get All Scan Reports</t>
+  </si>
+  <si>
+    <t>https://github.com/cadonuno/veracode-list-all-DAST-schedules</t>
+  </si>
+  <si>
+    <t>Veracode List All DAST Schedules</t>
+  </si>
+  <si>
+    <t>Lists the configured schedule for all DAST scans available to the current user</t>
+  </si>
+  <si>
+    <t>Scan Configuration, DAST, Automation Script</t>
+  </si>
+  <si>
+    <t>Veracode Get Sexpiring Grace Periods</t>
+  </si>
+  <si>
+    <t>https://github.com/cadonuno/veracode-get-expiring-grace-periods-java</t>
+  </si>
+  <si>
+    <t>Gets a list of expiring Grace Periods in the next X days (supports multiple intervals)</t>
+  </si>
+  <si>
+    <t>https://github.com/tjarrettveracode/veracode-pipeline-mitigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Retrieves findings with APPROVED mitigations from an application's policy scan (or sandbox) and creates a baseline file for Pipeline Scan. </t>
+  </si>
+  <si>
+    <t>Veracode Pipeline Mitigations</t>
+  </si>
+  <si>
+    <t>LLM Applications</t>
+  </si>
+  <si>
+    <t>Veracode Fix, SAST, AI, LLM, MCP</t>
+  </si>
+  <si>
+    <t>https://github.com/dipsylala/veracode-mcp</t>
+  </si>
+  <si>
+    <t>Veracode MCP</t>
+  </si>
+  <si>
+    <t>A Veracode MCP to help with packaging, pipeline scanning, and platform.</t>
+  </si>
+  <si>
+    <t>dipsylala</t>
+  </si>
+  <si>
+    <t>https://github.com/dipsylala</t>
+  </si>
+  <si>
+    <t>https://github.com/dipsylala/veracode-tui</t>
+  </si>
+  <si>
+    <t>Veracode Terminal User Interface</t>
+  </si>
+  <si>
+    <t>A Terminal User Interface (TUI) application for accessing Veracode's API, built with Go.</t>
+  </si>
+  <si>
+    <t>API wrappers, Veracode APIs, Go, CLI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2427,16 +2555,46 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF1F2328"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF59636E"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor theme="9" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -2444,15 +2602,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2842,19 +3018,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85512556-7A41-41CA-A994-088AF74D569E}">
-  <dimension ref="A1:G161"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G170"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="80.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="80.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="57.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="105.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="80.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="80.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="57.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="105.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2877,7 +3053,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -2900,7 +3076,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2923,7 +3099,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -2946,7 +3122,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -2969,7 +3145,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -2992,7 +3168,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -3015,7 +3191,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>37</v>
       </c>
@@ -3038,7 +3214,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -3061,7 +3237,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -3084,7 +3260,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>47</v>
       </c>
@@ -3107,7 +3283,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>51</v>
       </c>
@@ -3130,7 +3306,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -3153,7 +3329,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>61</v>
       </c>
@@ -3176,7 +3352,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>67</v>
       </c>
@@ -3199,7 +3375,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>73</v>
       </c>
@@ -3222,7 +3398,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>78</v>
       </c>
@@ -3245,7 +3421,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>82</v>
       </c>
@@ -3268,7 +3444,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>88</v>
       </c>
@@ -3291,7 +3467,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>92</v>
       </c>
@@ -3314,7 +3490,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>96</v>
       </c>
@@ -3337,7 +3513,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>102</v>
       </c>
@@ -3360,7 +3536,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>108</v>
       </c>
@@ -3383,7 +3559,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>114</v>
       </c>
@@ -3406,7 +3582,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>120</v>
       </c>
@@ -3429,7 +3605,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>126</v>
       </c>
@@ -3452,7 +3628,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>132</v>
       </c>
@@ -3475,7 +3651,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>138</v>
       </c>
@@ -3498,7 +3674,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>144</v>
       </c>
@@ -3521,7 +3697,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>150</v>
       </c>
@@ -3544,7 +3720,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>155</v>
       </c>
@@ -3567,7 +3743,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>160</v>
       </c>
@@ -3590,7 +3766,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>166</v>
       </c>
@@ -3613,7 +3789,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>172</v>
       </c>
@@ -3636,7 +3812,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>178</v>
       </c>
@@ -3659,7 +3835,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>184</v>
       </c>
@@ -3682,7 +3858,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>190</v>
       </c>
@@ -3705,7 +3881,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>195</v>
       </c>
@@ -3728,7 +3904,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>200</v>
       </c>
@@ -3751,7 +3927,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>206</v>
       </c>
@@ -3774,7 +3950,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>212</v>
       </c>
@@ -3797,7 +3973,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>218</v>
       </c>
@@ -3820,7 +3996,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>224</v>
       </c>
@@ -3843,7 +4019,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>228</v>
       </c>
@@ -3866,7 +4042,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>232</v>
       </c>
@@ -3889,7 +4065,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>160</v>
       </c>
@@ -3912,7 +4088,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>242</v>
       </c>
@@ -3935,7 +4111,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>246</v>
       </c>
@@ -3958,7 +4134,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>250</v>
       </c>
@@ -3981,7 +4157,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>255</v>
       </c>
@@ -4004,7 +4180,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>259</v>
       </c>
@@ -4027,7 +4203,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>263</v>
       </c>
@@ -4050,7 +4226,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>269</v>
       </c>
@@ -4073,7 +4249,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>273</v>
       </c>
@@ -4096,7 +4272,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>279</v>
       </c>
@@ -4119,7 +4295,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>284</v>
       </c>
@@ -4142,7 +4318,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>288</v>
       </c>
@@ -4165,7 +4341,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>292</v>
       </c>
@@ -4188,7 +4364,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>297</v>
       </c>
@@ -4211,7 +4387,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>301</v>
       </c>
@@ -4234,7 +4410,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>307</v>
       </c>
@@ -4257,7 +4433,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>313</v>
       </c>
@@ -4280,7 +4456,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>317</v>
       </c>
@@ -4303,7 +4479,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>323</v>
       </c>
@@ -4326,7 +4502,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>327</v>
       </c>
@@ -4349,7 +4525,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>331</v>
       </c>
@@ -4372,7 +4548,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>335</v>
       </c>
@@ -4395,7 +4571,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>340</v>
       </c>
@@ -4418,7 +4594,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>344</v>
       </c>
@@ -4441,7 +4617,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>348</v>
       </c>
@@ -4464,7 +4640,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>352</v>
       </c>
@@ -4487,7 +4663,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>357</v>
       </c>
@@ -4510,7 +4686,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>360</v>
       </c>
@@ -4533,7 +4709,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>363</v>
       </c>
@@ -4556,7 +4732,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>366</v>
       </c>
@@ -4579,7 +4755,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>369</v>
       </c>
@@ -4602,7 +4778,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>375</v>
       </c>
@@ -4625,7 +4801,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>381</v>
       </c>
@@ -4648,7 +4824,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>387</v>
       </c>
@@ -4671,7 +4847,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>393</v>
       </c>
@@ -4694,7 +4870,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>397</v>
       </c>
@@ -4717,7 +4893,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>401</v>
       </c>
@@ -4740,7 +4916,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>405</v>
       </c>
@@ -4763,7 +4939,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>408</v>
       </c>
@@ -4786,7 +4962,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>413</v>
       </c>
@@ -4809,7 +4985,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>415</v>
       </c>
@@ -4832,7 +5008,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>421</v>
       </c>
@@ -4855,7 +5031,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>426</v>
       </c>
@@ -4878,7 +5054,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>429</v>
       </c>
@@ -4901,7 +5077,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>435</v>
       </c>
@@ -4924,7 +5100,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>441</v>
       </c>
@@ -4947,7 +5123,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>445</v>
       </c>
@@ -4970,7 +5146,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>450</v>
       </c>
@@ -4993,7 +5169,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>455</v>
       </c>
@@ -5016,7 +5192,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>459</v>
       </c>
@@ -5039,7 +5215,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>463</v>
       </c>
@@ -5062,7 +5238,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>469</v>
       </c>
@@ -5085,7 +5261,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>473</v>
       </c>
@@ -5108,7 +5284,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>477</v>
       </c>
@@ -5131,7 +5307,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>480</v>
       </c>
@@ -5154,7 +5330,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>484</v>
       </c>
@@ -5177,7 +5353,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>490</v>
       </c>
@@ -5200,7 +5376,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>494</v>
       </c>
@@ -5223,7 +5399,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>498</v>
       </c>
@@ -5246,7 +5422,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>504</v>
       </c>
@@ -5269,7 +5445,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>508</v>
       </c>
@@ -5292,7 +5468,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>514</v>
       </c>
@@ -5315,7 +5491,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>520</v>
       </c>
@@ -5338,7 +5514,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>524</v>
       </c>
@@ -5361,7 +5537,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>528</v>
       </c>
@@ -5384,7 +5560,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>531</v>
       </c>
@@ -5407,7 +5583,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>534</v>
       </c>
@@ -5430,7 +5606,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>539</v>
       </c>
@@ -5453,7 +5629,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>543</v>
       </c>
@@ -5476,7 +5652,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>548</v>
       </c>
@@ -5499,7 +5675,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>552</v>
       </c>
@@ -5522,7 +5698,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>558</v>
       </c>
@@ -5545,7 +5721,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>562</v>
       </c>
@@ -5568,7 +5744,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>568</v>
       </c>
@@ -5591,7 +5767,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>572</v>
       </c>
@@ -5614,7 +5790,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>576</v>
       </c>
@@ -5637,7 +5813,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>580</v>
       </c>
@@ -5660,7 +5836,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>586</v>
       </c>
@@ -5683,7 +5859,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>694</v>
       </c>
@@ -5706,7 +5882,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>699</v>
       </c>
@@ -5729,7 +5905,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>705</v>
       </c>
@@ -5752,7 +5928,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>711</v>
       </c>
@@ -5775,7 +5951,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>718</v>
       </c>
@@ -5798,7 +5974,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>721</v>
       </c>
@@ -5821,7 +5997,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>592</v>
       </c>
@@ -5844,7 +6020,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>598</v>
       </c>
@@ -5867,7 +6043,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>602</v>
       </c>
@@ -5890,7 +6066,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>608</v>
       </c>
@@ -5913,7 +6089,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>613</v>
       </c>
@@ -5936,7 +6112,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>619</v>
       </c>
@@ -5959,7 +6135,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>623</v>
       </c>
@@ -5982,7 +6158,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>629</v>
       </c>
@@ -6005,7 +6181,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>635</v>
       </c>
@@ -6028,7 +6204,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>639</v>
       </c>
@@ -6051,7 +6227,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>642</v>
       </c>
@@ -6074,7 +6250,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>645</v>
       </c>
@@ -6097,7 +6273,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>649</v>
       </c>
@@ -6120,7 +6296,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>653</v>
       </c>
@@ -6143,7 +6319,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>657</v>
       </c>
@@ -6166,7 +6342,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>661</v>
       </c>
@@ -6189,7 +6365,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>664</v>
       </c>
@@ -6212,7 +6388,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>668</v>
       </c>
@@ -6235,7 +6411,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>671</v>
       </c>
@@ -6258,7 +6434,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>674</v>
       </c>
@@ -6281,7 +6457,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>734</v>
       </c>
@@ -6304,7 +6480,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
         <v>742</v>
       </c>
@@ -6327,7 +6503,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="1" t="s">
         <v>735</v>
       </c>
@@ -6350,7 +6526,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>746</v>
       </c>
@@ -6373,7 +6549,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
         <v>749</v>
       </c>
@@ -6396,7 +6572,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
         <v>757</v>
       </c>
@@ -6419,7 +6595,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>760</v>
       </c>
@@ -6442,7 +6618,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
         <v>764</v>
       </c>
@@ -6465,7 +6641,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
         <v>769</v>
       </c>
@@ -6488,7 +6664,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>773</v>
       </c>
@@ -6511,7 +6687,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
         <v>778</v>
       </c>
@@ -6534,7 +6710,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="1" t="s">
         <v>781</v>
       </c>
@@ -6555,6 +6731,213 @@
       </c>
       <c r="G161" t="s">
         <v>690</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A162" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>789</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>790</v>
+      </c>
+      <c r="D162" s="5" t="s">
+        <v>787</v>
+      </c>
+      <c r="E162" t="s">
+        <v>448</v>
+      </c>
+      <c r="F162" t="s">
+        <v>420</v>
+      </c>
+      <c r="G162" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A163" s="5" t="s">
+        <v>791</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>793</v>
+      </c>
+      <c r="D163" s="5" t="s">
+        <v>787</v>
+      </c>
+      <c r="E163" t="s">
+        <v>448</v>
+      </c>
+      <c r="F163" t="s">
+        <v>798</v>
+      </c>
+      <c r="G163" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A164" s="5" t="s">
+        <v>794</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="D164" s="5" t="s">
+        <v>787</v>
+      </c>
+      <c r="E164" t="s">
+        <v>448</v>
+      </c>
+      <c r="F164" t="s">
+        <v>797</v>
+      </c>
+      <c r="G164" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A165" s="5" t="s">
+        <v>799</v>
+      </c>
+      <c r="B165" s="6" t="s">
+        <v>801</v>
+      </c>
+      <c r="C165" s="6" t="s">
+        <v>800</v>
+      </c>
+      <c r="D165" s="5" t="s">
+        <v>787</v>
+      </c>
+      <c r="E165" t="s">
+        <v>448</v>
+      </c>
+      <c r="F165" t="s">
+        <v>412</v>
+      </c>
+      <c r="G165" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A166" s="5" t="s">
+        <v>802</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>803</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>804</v>
+      </c>
+      <c r="D166" s="5" t="s">
+        <v>787</v>
+      </c>
+      <c r="E166" t="s">
+        <v>448</v>
+      </c>
+      <c r="F166" t="s">
+        <v>805</v>
+      </c>
+      <c r="G166" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A167" s="5" t="s">
+        <v>807</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>806</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>808</v>
+      </c>
+      <c r="D167" s="5" t="s">
+        <v>787</v>
+      </c>
+      <c r="E167" t="s">
+        <v>448</v>
+      </c>
+      <c r="F167" t="s">
+        <v>412</v>
+      </c>
+      <c r="G167" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A168" t="s">
+        <v>809</v>
+      </c>
+      <c r="B168" t="s">
+        <v>811</v>
+      </c>
+      <c r="C168" t="s">
+        <v>810</v>
+      </c>
+      <c r="D168" t="s">
+        <v>58</v>
+      </c>
+      <c r="E168" t="s">
+        <v>76</v>
+      </c>
+      <c r="F168" t="s">
+        <v>412</v>
+      </c>
+      <c r="G168" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" ht="16" x14ac:dyDescent="0.45">
+      <c r="A169" t="s">
+        <v>814</v>
+      </c>
+      <c r="B169" t="s">
+        <v>815</v>
+      </c>
+      <c r="C169" t="s">
+        <v>816</v>
+      </c>
+      <c r="D169" s="7" t="s">
+        <v>817</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="F169" t="s">
+        <v>813</v>
+      </c>
+      <c r="G169" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" ht="16" x14ac:dyDescent="0.45">
+      <c r="A170" t="s">
+        <v>819</v>
+      </c>
+      <c r="B170" t="s">
+        <v>820</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="D170" s="7" t="s">
+        <v>817</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="F170" t="s">
+        <v>822</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>698</v>
       </c>
     </row>
   </sheetData>
@@ -6578,10 +6961,12 @@
     <hyperlink ref="E158" r:id="rId17" xr:uid="{7FA1CF51-B708-4714-A473-4A74EFB45D49}"/>
     <hyperlink ref="E159" r:id="rId18" xr:uid="{25B2D764-9A33-4D76-84FC-FBC93F92D7D1}"/>
     <hyperlink ref="E161" r:id="rId19" xr:uid="{A3352317-67B8-9840-A607-9919847AA0FB}"/>
+    <hyperlink ref="E169" r:id="rId20" xr:uid="{9860411D-B3DF-4915-AC0A-89F06AE0E326}"/>
+    <hyperlink ref="E170" r:id="rId21" xr:uid="{2296F52F-B576-4EA5-B077-C3295A9EC58E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId20"/>
+    <tablePart r:id="rId22"/>
   </tableParts>
 </worksheet>
 </file>
@@ -6590,6 +6975,23 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="616b837b-4f10-4907-bd91-1587e7ce931b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D88478712453E44F921675445F4DEED5" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1f7ff3b011b4c354fea863625355c509">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="616b837b-4f10-4907-bd91-1587e7ce931b" xmlns:ns4="6517f0ec-21e4-436e-b84f-408b51251641" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3b9772cf3c1eb2c6c54f90122974c49d" ns3:_="" ns4:_="">
     <xsd:import namespace="616b837b-4f10-4907-bd91-1587e7ce931b"/>
@@ -6822,23 +7224,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="616b837b-4f10-4907-bd91-1587e7ce931b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EB1E18A-FD49-44B6-BB37-CF64EAE6DAD6}">
   <ds:schemaRefs>
@@ -6848,6 +7233,31 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D990C314-942E-4A4C-8C35-1591F3BBFBCC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6517f0ec-21e4-436e-b84f-408b51251641"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="616b837b-4f10-4907-bd91-1587e7ce931b"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6B177E5-9F9F-4535-B0EA-B4A85808813C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51B172E4-8F9B-4969-9A78-7CEF326A2DFD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6866,27 +7276,8 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6B177E5-9F9F-4535-B0EA-B4A85808813C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D990C314-942E-4A4C-8C35-1591F3BBFBCC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6517f0ec-21e4-436e-b84f-408b51251641"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="616b837b-4f10-4907-bd91-1587e7ce931b"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{3b627b68-f21c-4ed7-9fe3-698efdedbe21}" enabled="0" method="" siteId="{3b627b68-f21c-4ed7-9fe3-698efdedbe21}" removed="1"/>
+</clbl:labelList>
 </file>